--- a/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,225 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26MBR</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502545309</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI N.K.P BÀ RỊA</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Hương Lộ 2, Tổ 17, Ấp Bắc 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13" t="n">
+        <v>1.747725E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>1747725.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>1.9224975E7</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26MKL</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502553204</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI KIM LÂN</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8, Ấp 2, Xã Hòa Hội, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Trương Đỗ Lưu (HKD Hùng Mạnh)</t>
+        </is>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13" t="n">
+        <v>2.1256649E7</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>2100851.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>2.33575E7</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C26MKL</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>5887</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502553204</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI KIM LÂN</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8, Ấp 2, Xã Hòa Hội, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Trương Đỗ Lưu (HKD Hùng Mạnh)</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>3.5763637E7</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>3576363.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>3.934E7</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
